--- a/www/download/COUNTRY.MLT.rpO2.xlsx
+++ b/www/download/COUNTRY.MLT.rpO2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.821684755536959</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.839100636076563</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.898078280441284</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.904384898541739</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.929851826238597</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.01871863654664</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.04756224641374</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.00792264839678</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.877192137997102</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.802021683764487</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.804162377075274</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.793408381912368</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.724495030641948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.679660773115357</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.716576242819136</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>-0.177776711731779</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>-0.304849409764347</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.519582353724271</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>-0.100638243919666</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>-0.393251558518548</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>-0.498273934955808</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>-0.718761082076456</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>-0.702085077069407</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>-0.648171855432111</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>-0.649852110084348</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>-0.621953808873413</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>-0.654600281230949</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>-0.539323326557277</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>-0.452890055159163</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>-0.242705129434814</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.34138689321345</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.137520836429634</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1.50177125647451</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.487525926675904</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>-0.00589542333688231</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>-0.181744678369102</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>-0.536219051360297</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>-0.509991172002829</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>-0.394900610763516</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>-0.434234964145016</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>-0.378958923379925</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>-0.440076477513249</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>-0.255830717314234</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>-0.13180706249319</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>0.20983458963979</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>272.138</t>
+          <t>0.612753675980358</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>273.341</t>
+          <t>0.357662233849417</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>274.43</t>
+          <t>1.95978314054804</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>278.239</t>
+          <t>0.748269831001178</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>282.002</t>
+          <t>0.183153618574388</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>285.185</t>
+          <t>-0.0209179692931829</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>244.532</t>
+          <t>-0.44970835588207</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>288.899</t>
+          <t>-0.415142521319904</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>277.161</t>
+          <t>-0.536927793744111</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>-0.332038675329906</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>286.041</t>
+          <t>-0.269330205548013</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>287.987</t>
+          <t>-0.332649582184596</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>300.123</t>
+          <t>-0.132623031097158</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>306.883</t>
+          <t>0.0145436104728449</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>307.78</t>
+          <t>0.411057245817918</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>239.98</t>
+          <t>11167724456.4558</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>241.04</t>
+          <t>11163940638.9487</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>242.001</t>
+          <t>6826085919.28434</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>245.359</t>
+          <t>9476459582.43561</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>248.678</t>
+          <t>15474864678.9609</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>251.485</t>
+          <t>27289162361.1751</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>17055773362.3811</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>256.499</t>
+          <t>16316234410.3498</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>245.286</t>
+          <t>17971113825.7043</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>250.577</t>
+          <t>16594031284.3506</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>252.301</t>
+          <t>19964650316.2471</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>253.898</t>
+          <t>20938264650.8959</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>264.56</t>
+          <t>16887529808.0695</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>271.437</t>
+          <t>16951807619.2244</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>264.649</t>
+          <t>11035515554.8305</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>1900667004.63341</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>2258405623.1356</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>1519333738.02462</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>1822588255.00138</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>2881066521.66669</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>3706797631.50566</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>4431673107.57078</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>4875552308.91768</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>5265920222.75714</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>4464886008.54102</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>5606358448.97883</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>5065564556.22753</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>4200697542.65662</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>4566551003.27009</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>3136956623.919</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>49760852.5583581</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>54380380.6848098</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>37274166.6265925</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>41342600.2944344</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>61386148.6257488</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>80584195.0080519</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>69885653.1207879</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>68120444.5595706</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>62042522.2725739</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>53682419.8206142</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>63756549.185154</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>60744279.382343</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>45980126.1618075</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>41333680.3436771</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>33695335.5192469</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>670.095580525825</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>685.566144631023</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>661.623197322073</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>660.013429463111</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>602.017022511818</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>439.540219390927</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>360.046405350247</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>448.931916281442</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>449.114484766017</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>478.596800838737</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>626.74665015986</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>530.953761994801</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>719.958427611294</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>848.73183213291</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>985.059577989296</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>4681.93584166209</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>4860.02575588441</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>2927.21143521836</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>3997.09466950973</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>6.88</t>
+          <t>6078.10457329677</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6.99</t>
+          <t>8453.47508352882</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>5025.46524192674</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.24</t>
+          <t>5051.93505074739</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5688.99508582677</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>5674.1374650319</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>6599.1327435635</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>7334.66734360518</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>10.54</t>
+          <t>7539.19277625767</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>8468.09547851385</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>6366.73544617646</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>0.397760069994671</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15.58</t>
+          <t>0.172937018538225</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>1.58255815142108</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.542225954197174</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15.27</t>
+          <t>0.0356471359852502</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>-0.146608665358656</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>16.31</t>
+          <t>-0.521556804812164</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>-0.493381947561077</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>16.65</t>
+          <t>-0.535508914408002</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>-0.435082593528122</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>-0.387358366276398</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>-0.445315624958443</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>-0.274735283644091</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>18.44</t>
+          <t>-0.144636132145851</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20.22</t>
+          <t>0.170710551313173</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>77.21</t>
+          <t>935.033766716748</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>76.59</t>
+          <t>962.436088886035</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>878.112097574302</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>79.18</t>
+          <t>988.361789538299</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>77.84</t>
+          <t>1028.45972006696</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>1079.4579623307</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>76.76</t>
+          <t>862.927322251072</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.52</t>
+          <t>857.643554506389</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>1092.12927592513</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>73.21</t>
+          <t>1192.83169298121</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>72.36</t>
+          <t>1235.83258064407</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>71.13</t>
+          <t>1428.20462482944</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>71.26</t>
+          <t>1649.43198151582</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>70.05</t>
+          <t>1868.92749049352</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>67.76</t>
+          <t>1817.72581885165</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.821684755536959</t>
+          <t>15520.2434150722</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.839100636076563</t>
+          <t>18360.2722979033</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.898078280441284</t>
+          <t>12302.7654452112</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.904384898541739</t>
+          <t>14556.3607016884</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.929851826238597</t>
+          <t>22702.9587443162</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.01871863654664</t>
+          <t>28883.7462172355</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.04756224641374</t>
+          <t>33631.1248036277</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00792264839678</t>
+          <t>36288.7517187865</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.877192137997102</t>
+          <t>39515.0061578246</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.802021683764487</t>
+          <t>34003.9984613592</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.804162377075274</t>
+          <t>42115.7480982574</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.793408381912368</t>
+          <t>37263.2980594032</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.724495030641948</t>
+          <t>29949.8204709774</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679660773115357</t>
+          <t>31821.8208669202</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716576242819136</t>
+          <t>21710.1643608373</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>937922675.992764</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1840483280.0563</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>457006532.666421</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1153595607.99338</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3300627427.24837</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>5552981807.88612</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>5065774768.35161</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>6550285914.19552</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>5860291519.26784</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4269324936.17152</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>7607457662.88317</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>6955744486.44899</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>6120558755.87395</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>6794048124.8627</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>4415142111.57783</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-77236359.2398778</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>734966395.908636</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-588904171.493733</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-79539173.5736783</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1472657688.70538</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2715368765.09965</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>2988371003.05873</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3815913096.98117</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3252619225.47222</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1391526094.61915</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>4368243352.68233</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3454448105.64925</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2423515475.95532</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2457821210.11207</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1075800784.15281</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1015159035.23264</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1105516884.14767</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>1045910704.16015</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1233134781.56706</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1827969738.54299</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2837613042.78648</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>2077403765.29288</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>2734372817.21436</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>2607672293.79562</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>2877798841.55236</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>3239214310.20084</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>3501296380.79974</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>3697043279.91863</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>4336226914.75063</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>3339341327.42502</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>21693.5765221856</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>21535.4430486527</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>31772.6071855518</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>22449.1972727997</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>23512.2542019423</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>24649.1387337685</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>16090.5828088085</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>18384.5367212113</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>18354.3681074224</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>19209.4506204648</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>25801.8607204081</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>20669.3691960673</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>21721.5480487938</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>27219.2357788907</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>25416.3184879754</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>21767.009359771</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>21605.3263407806</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>21226.9439000765</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>21132.7809371624</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>20548.7073529483</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>19058.2591818137</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>16119.5110509689</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>18427.0614782833</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>18386.7065640895</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>19292.9342643022</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>25924.3348830028</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>20775.8565146235</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>21838.9404027287</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>20501.6118390344</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>22046.2476379373</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-17.78</t>
+          <t>2183.75432366237</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-30.48</t>
+          <t>2112.65111979316</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>51.96</t>
+          <t>2044.26726001742</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>2297.17374123947</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-39.33</t>
+          <t>2486.67624060495</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-49.83</t>
+          <t>2847.25664877912</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-71.88</t>
+          <t>2432.65066122194</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-70.21</t>
+          <t>2722.81729745513</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-64.82</t>
+          <t>3059.03083731146</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-64.99</t>
+          <t>3345.33148452363</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-62.2</t>
+          <t>3577.48983631473</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>-65.46</t>
+          <t>4339.13982305009</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>-53.93</t>
+          <t>5320.73796135974</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>-45.29</t>
+          <t>5961.29617365826</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-24.27</t>
+          <t>4978.86495064032</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>34.14</t>
+          <t>5138246827.41501</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>4882058674.043</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>150.18</t>
+          <t>2921737705.57789</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>48.75</t>
+          <t>4760778737.47346</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>8227373195.55899</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-18.17</t>
+          <t>16306926908.6901</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-53.62</t>
+          <t>9242603067.91276</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-51</t>
+          <t>8415619557.59367</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-39.49</t>
+          <t>8935225035.83883</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-43.42</t>
+          <t>8074937873.10877</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-37.9</t>
+          <t>8219456695.75731</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>10338041532.1428</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-25.58</t>
+          <t>7973323152.43598</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-13.18</t>
+          <t>7539820926.73635</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>4639837609.7432</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>61.28</t>
+          <t>3077.55815565765</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>2989.78848671855</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>195.98</t>
+          <t>2760.72266341456</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>74.83</t>
+          <t>2924.43956971278</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>18.32</t>
+          <t>3136.08578646415</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>3538.13613509204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>2954.38987457375</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-41.51</t>
+          <t>3079.71544903443</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-53.69</t>
+          <t>3638.92937598667</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-33.2</t>
+          <t>4078.39464551972</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-26.93</t>
+          <t>4367.58618560208</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-33.26</t>
+          <t>5158.88821386639</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-13.26</t>
+          <t>6223.19467713802</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>6853.35799509956</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>41.11</t>
+          <t>5595.79028406079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3022.881</t>
+          <t>9777073559.88116</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3013.689</t>
+          <t>10205461909.3443</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2972.711</t>
+          <t>5839295765.97114</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3000.594</t>
+          <t>8269547849.06144</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2957.128</t>
+          <t>14728496978.0239</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2773.597</t>
+          <t>26715483426.895</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2394.049</t>
+          <t>18238395156.8058</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2788.483</t>
+          <t>17541556050.3726</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2768.691</t>
+          <t>18812123004.2117</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2871.148</t>
+          <t>16999801173.73</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3912.492</t>
+          <t>21094189487.7613</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3203.459</t>
+          <t>22375121421.9594</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3474.834</t>
+          <t>18257458446.7403</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>3358.98</t>
+          <t>17930828462.958</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>3581.774</t>
+          <t>11054995989.4258</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2656.676</t>
+          <t>-893.803831995282</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2648.968</t>
+          <t>-877.137366925392</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3923.768</t>
+          <t>-716.455403397146</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2810.843</t>
+          <t>-627.265828473319</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2983.768</t>
+          <t>-649.409545859193</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3163.349</t>
+          <t>-690.879486312916</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2120.304</t>
+          <t>-521.739213351805</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2470.043</t>
+          <t>-356.898151579299</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2445.973</t>
+          <t>-579.898538675215</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2522.292</t>
+          <t>-733.063160996098</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>3434.689</t>
+          <t>-790.096349287349</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2809.79</t>
+          <t>-819.748390816298</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>3046.618</t>
+          <t>-902.456715778277</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>3906.063</t>
+          <t>-892.061821441303</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>3672.468</t>
+          <t>-616.925333420476</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11167.724</t>
+          <t>-4638826732.46615</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11163.941</t>
+          <t>-5323403235.30131</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6826.086</t>
+          <t>-2917558060.39324</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9476.46</t>
+          <t>-3508769111.58799</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>15474.865</t>
+          <t>-6501123782.46491</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>27289.162</t>
+          <t>-10408556518.2049</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>17055.773</t>
+          <t>-8995792088.89304</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>16316.234</t>
+          <t>-9125936492.77892</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>17971.114</t>
+          <t>-9876897968.37288</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>16594.031</t>
+          <t>-8924863300.62124</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>19964.65</t>
+          <t>-12874732792.004</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>20938.265</t>
+          <t>-12037079889.8166</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>16887.53</t>
+          <t>-10284135294.3043</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>16951.808</t>
+          <t>-10391007536.2217</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11035.516</t>
+          <t>-6415158379.68256</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1385.82335</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1423.35312</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1377.26698</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>1476.38768</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1473.61581</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1515.93832</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1418.21509</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>1626.93416</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1868.283</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1984.44397</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2041.98878</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2193.14696</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2538.99753</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>2825.1127</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>2576.19549</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1598.365</t>
+          <t>0.0408082018147764</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1574.811</t>
+          <t>0.0376896455875792</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1542.867</t>
+          <t>0.0495962516759357</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1564.784</t>
+          <t>0.0447526145337143</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1532.736</t>
+          <t>0.0405197614288493</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1418.906</t>
+          <t>0.0421049528694169</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1221.951</t>
+          <t>0.0469073191731178</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1449.915</t>
+          <t>0.0580598351060868</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1418.719</t>
+          <t>0.0485127775549195</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1399.658</t>
+          <t>0.0429817634714068</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1896.125</t>
+          <t>0.0518902133423115</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1515.713</t>
+          <t>0.0427299673264274</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1612.682</t>
+          <t>0.051520688176504</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1699.029</t>
+          <t>0.0377331288637923</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1707.412</t>
+          <t>0.0303310725219007</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1616.02247943738</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1715.50960720146</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1667.34448396809</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1754.22786698853</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1785.88735535493</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1708.42222994882</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1795.89572328168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1963.83622744647</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2341.0084328578</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2657.18545419359</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2726.00838892361</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2910.50556607688</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>3330.69237946551</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>4211.27127438239</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>3969.63156938789</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1900.667</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2258.406</t>
+          <t>1951.70874750034</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1519.334</t>
+          <t>1896.64032042978</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1822.588</t>
+          <t>1995.10864087904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2881.067</t>
+          <t>2031.06693944933</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3706.798</t>
+          <t>1942.8079854763</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4431.673</t>
+          <t>2027.75751254768</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4875.552</t>
+          <t>2217.01603428793</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5265.92</t>
+          <t>2649.87773934298</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4464.886</t>
+          <t>3024.69870145227</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>5606.358</t>
+          <t>3105.22631611993</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>5065.565</t>
+          <t>3318.28575340782</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>4200.698</t>
+          <t>3798.83718075924</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>4566.551</t>
+          <t>4801.04665285912</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3136.957</t>
+          <t>4526.25911690874</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>10387.5856369219</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>10472.6167481845</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>158.26</t>
+          <t>9483.38162869941</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>10201.0690177384</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>10220.2398503971</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-14.66</t>
+          <t>10254.1775437209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-52.16</t>
+          <t>10625.9934267763</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-49.34</t>
+          <t>11585.0704704321</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-53.55</t>
+          <t>13726.6270515646</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>15507.6288577581</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-38.74</t>
+          <t>15925.640501504</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-44.53</t>
+          <t>17769.8778930057</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-27.47</t>
+          <t>21012.7662506392</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>24984.4029645788</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>24997.3651176415</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>49.761</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>54.38</t>
+          <t>1971.81963499446</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>37.274</t>
+          <t>2014.16080919266</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41.343</t>
+          <t>2105.0491934226</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>61.386</t>
+          <t>2187.32487864978</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>80.584</t>
+          <t>2220.06132249716</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>69.886</t>
+          <t>2341.96233993632</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>68.12</t>
+          <t>2416.85037926708</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>62.043</t>
+          <t>2406.06824787509</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>53.682</t>
+          <t>2461.64909418327</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>63.757</t>
+          <t>2512.31847011829</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>60.744</t>
+          <t>2574.27894368699</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>45.98</t>
+          <t>2626.41985086363</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>41.334</t>
+          <t>3048.45170473549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>33.695</t>
+          <t>2961.89450481308</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1616.02247943738</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1733.12184215755</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1770.48890676647</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1850.65172602171</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1922.98613329567</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1951.74472640863</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2073.73783740309</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2140.18170002683</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2124.94077630928</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2160.56270123431</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2203.17336956751</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2255.01404420631</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2299.23424464493</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2670.20692419726</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2593.97155767355</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1358.93245775653</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1357.14530249966</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1348.45227957022</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1444.88629912096</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1442.58140055067</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1511.2096245237</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1361.36418745232</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1530.27083571207</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1758.04608065702</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1859.37692854773</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2062.21746388007</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2187.51092659218</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2732.02415924076</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2811.66718714088</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2575.92271309126</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2656676445.43296</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2648967558.25063</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3923767729.86454</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2810842910.67806</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2983768291.74709</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>3163348977.99599</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2120303841.61417</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2470042815.30797</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>2445973000.90932</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2522291824.13757</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>3434688599.42251</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2809789510.10373</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>3046617711.77182</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>3906062728.91035</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>3672468218.63372</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3022881380.87258</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3013689421.25384</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2972711369.97767</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>3000594053.02064</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2957128300.21702</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2773597387.95884</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2394048823.64792</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2788483301.39827</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2768691182.47097</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2871148038.65578</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>3912491784.66955</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>3203458742.74327</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>3474834454.95969</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>3358980160.0876</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>3581773648.17589</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1598365089.97196</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1574810531.2954</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1542866612.49504</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1564784200.85533</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1532736372.90321</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1418905750.91379</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1221950524.7716</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1449915390.19328</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>1418719370.42281</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1399657716.19942</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>1896124565.69013</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1515712964.9143</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>1612681857.02127</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>1699028875.51688</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1707411967.59856</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>138874.446687167</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>139488.262001645</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>140044.246782362</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>141987.657087953</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>143908.239551269</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>145532.567350409</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>148518.699858705</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>151325.446256559</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>150581.137128626</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>148818.629624851</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>150919.65916683</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>154191.416391832</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>159111.861238722</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>163839.80861896</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>162466.36194054</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>122463.736798588</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>123005.017926314</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>123495.302319692</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>125209.060997641</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>126902.689385716</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>128335.071345203</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>131772.967257186</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>134354.368171712</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>133263.808734455</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>131304.73504799</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>133117.864507571</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>135939.780428245</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>140257.853856829</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>143503.761848436</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>144492.532243455</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>272137948.345955</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>273340778.991406</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>274430285.096707</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>278238586.090692</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>282002153.713565</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>285185181.586899</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>244531553.853267</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>288899268.348295</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>277160855.202434</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>284000169.133413</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>286041214.56216</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>287986878.933645</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>300122877.824299</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>306882575.853023</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>307779660.295915</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>239979570.570101</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>241040263.441192</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>242001023.264924</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>245359299.619592</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>248678128.718725</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>251485020.101561</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>216960210.868469</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>256499350.402692</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>245286440.92271</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>250577276.888324</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>252301097.510267</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>253897875.799843</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>264559728.038222</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>271436883.391728</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>264648734.990132</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.0785096043442988</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.0783260088229312</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.0725635829408859</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.0671800623138325</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.0688251783923756</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.0699078324120806</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.0692388796418979</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.0724385050920685</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.0880048178129122</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.0921735966508009</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.0974095903387319</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.101508629331494</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.105364824723641</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.115065358467651</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.120196730948339</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.149374382655247</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.155770502716519</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.148432965518307</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.141043625728438</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.152727722560584</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.156792418524991</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.163142546644421</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.162375411188584</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.16653267978683</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.175757286429952</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.179013652283156</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.187159780642293</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.182028895279162</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.18440883981998</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.202179913289584</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.772116013000455</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.76590348846055</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.779003451540807</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.79177631195773</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.77844709904704</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.773299749062929</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.767618573713681</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.765186083719348</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.745462502400258</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.732069116919247</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.723576757378112</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.711331590026213</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.712606279997197</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.700525801712369</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.677623355762077</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6810.28788</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6759.79225</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6504.52899</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>7022.21424</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7201.39947</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7612.00423</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7085.95531</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7660.96435</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>9137.04683</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>10679.72391</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>11410.39724</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>12906.4076</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>15298.69514</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>17266.45712</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>16001.56341</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3197.71274</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3308.85405</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3245.0926</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3439.99494</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3473.64834</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3454.01761</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3389.1217</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3747.28687</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4407.92382</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4884.07563</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5167.44378</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5505.79668</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6530.86134</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>7612.71384</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7102.18183</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8540.10449177539</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8906.54079634492</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>9298.47153182451</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9715.44255502075</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>10129.7218552802</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10575.0429322389</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10878.9484176219</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11000.1283463253</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>11266.8232314971</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>11529.1787391199</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>11932.1325426299</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>12320.7451710381</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>12719.6954845692</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>12822.9626287163</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>12793.4869850017</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
